--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260902.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>179,141,000</t>
+          <t>922,437,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.55%</t>
+          <t>9.63%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>919,737,000</t>
+          <t>179,341,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.54%</t>
+          <t>9.47%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>375,940,486</t>
+          <t>378,840,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>39,360,000</t>
+          <t>39,460,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.20%</t>
+          <t>6.25%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.01%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>190,201,000</t>
+          <t>604,027,270</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.90%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>604,027,270</t>
+          <t>190,401,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,117,000</t>
+          <t>5,142,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>27,629,000</t>
+          <t>27,829,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>132,826,945</t>
+          <t>449,396,250</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>451,396,250</t>
+          <t>132,826,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>355,020,964</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -946,24 +946,24 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,461,000</t>
+          <t>84,590,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,95 +985,95 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>233,408,056</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>84,290,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,598,442</t>
+          <t>196,411,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>197,061,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,605,000</t>
+          <t>35,705,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -1161,78 +1161,78 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>190,453,000</t>
+          <t>191,053,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,388,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>53,588,000</t>
+          <t>254,199,845</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>255,099,845</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1249,51 +1249,47 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>89,780,061</t>
+          <t>89,630,061</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>A97102</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>97央債甲2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,986,000</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
-      </c>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>A97102</t>
+          <t>B618CW</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>97央債甲2</t>
+          <t>P11台積1B</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1301,17 +1297,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>B618CW</t>
+          <t>B95553</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>P11台積1B</t>
+          <t>P08凱控1B</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1319,17 +1315,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>B95553</t>
+          <t>B95555</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1B</t>
+          <t>P09凱控1B</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>185,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -1337,17 +1333,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>B96525</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>P11元金2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>120,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -1355,17 +1351,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>B96525</t>
+          <t>B97872</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>P11元金2</t>
+          <t>P13富邦金1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>120,000,000</t>
+          <t>45,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -1373,17 +1369,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>B97872</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>P13富邦金1</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>45,000,000</t>
+          <t>31,598,741,347</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -1391,17 +1387,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>31,076,203,859</t>
+          <t>5,184,742,226</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -1409,38 +1405,20 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>5,591,475,826</t>
+          <t>-607,144,928</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>-134,132,350</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
